--- a/results/reliability_eval/Llama-3-8B_P159_sample_30_tokens_0.1_temp_direct_query_scores_08-24-4.xlsx
+++ b/results/reliability_eval/Llama-3-8B_P159_sample_30_tokens_0.1_temp_direct_query_scores_08-24-4.xlsx
@@ -477,31 +477,31 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0.5613997719113739</v>
+        <v>0.4676507650765076</v>
       </c>
       <c r="B2" t="n">
-        <v>0.6971511562004108</v>
+        <v>0.4685935914254118</v>
       </c>
       <c r="C2" t="n">
-        <v>0.5614552409352522</v>
+        <v>0.4676527652765277</v>
       </c>
       <c r="D2" t="n">
-        <v>0.6971594508139569</v>
+        <v>0.4685935914254118</v>
       </c>
       <c r="E2" t="n">
-        <v>0.4260864163016805</v>
+        <v>0.5397499749974997</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6159198102789258</v>
+        <v>0.5200700915088293</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9993765281716078</v>
+        <v>0.9962696269626963</v>
       </c>
       <c r="H2" t="n">
-        <v>0.999578524718191</v>
+        <v>0.9949609836198334</v>
       </c>
       <c r="I2" t="n">
-        <v>0.657</v>
+        <v>0.495</v>
       </c>
     </row>
   </sheetData>
